--- a/output/总表.xlsx
+++ b/output/总表.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>刘羽佳</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -22323,7 +22323,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -24249,7 +24249,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -27980,7 +27980,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28515,7 +28515,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -35898,7 +35898,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -36754,7 +36754,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -39964,7 +39964,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -40392,7 +40392,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -40499,7 +40499,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -41355,7 +41355,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -41890,7 +41890,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -42197,7 +42197,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -42946,7 +42946,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -43267,7 +43267,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -43374,7 +43374,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -44016,7 +44016,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -45500,7 +45500,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -45714,7 +45714,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -45821,7 +45821,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -46142,7 +46142,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -46249,7 +46249,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -46356,7 +46356,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -46891,7 +46891,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -47426,7 +47426,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -47961,7 +47961,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -48496,7 +48496,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -49994,7 +49994,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -50101,7 +50101,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -50850,7 +50850,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -51813,7 +51813,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -52027,7 +52027,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -52134,7 +52134,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -52348,7 +52348,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -53418,7 +53418,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -53525,7 +53525,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -53632,7 +53632,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -55023,7 +55023,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -55237,7 +55237,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -56521,7 +56521,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -57591,7 +57591,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D535" t="n">
@@ -57698,7 +57698,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -57805,7 +57805,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -58233,7 +58233,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -58554,7 +58554,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -59624,7 +59624,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -59731,7 +59731,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -59838,7 +59838,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -59945,7 +59945,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -60052,7 +60052,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D558" t="n">
@@ -60159,7 +60159,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -61015,7 +61015,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -61764,7 +61764,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -61871,7 +61871,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D587" t="n">
@@ -63369,7 +63369,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D589" t="n">
@@ -63583,7 +63583,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D591" t="n">
@@ -64011,7 +64011,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D595" t="n">
@@ -64118,7 +64118,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D596" t="n">
@@ -65295,7 +65295,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D607" t="n">
@@ -67756,7 +67756,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D630" t="n">
